--- a/etf_holdings/2026-10-14_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:17</t>
+          <t>2026-10-14 00:25:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:17</t>
+          <t>2026-10-14 00:25:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:17</t>
+          <t>2026-10-14 00:25:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:17</t>
+          <t>2026-10-14 00:25:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:17</t>
+          <t>2026-10-14 00:25:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:17</t>
+          <t>2026-10-14 00:25:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:17</t>
+          <t>2026-10-14 00:25:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:17</t>
+          <t>2026-10-14 00:25:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:17</t>
+          <t>2026-10-14 00:25:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:17</t>
+          <t>2026-10-14 00:25:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:17</t>
+          <t>2026-10-14 00:25:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:17</t>
+          <t>2026-10-14 00:25:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:17</t>
+          <t>2026-10-14 00:25:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:17</t>
+          <t>2026-10-14 00:25:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:17</t>
+          <t>2026-10-14 00:25:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:19</t>
+          <t>2026-10-14 00:25:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:19</t>
+          <t>2026-10-14 00:25:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:19</t>
+          <t>2026-10-14 00:25:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:19</t>
+          <t>2026-10-14 00:25:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:19</t>
+          <t>2026-10-14 00:25:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:19</t>
+          <t>2026-10-14 00:25:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:19</t>
+          <t>2026-10-14 00:25:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:19</t>
+          <t>2026-10-14 00:25:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:19</t>
+          <t>2026-10-14 00:25:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:19</t>
+          <t>2026-10-14 00:25:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:19</t>
+          <t>2026-10-14 00:25:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:19</t>
+          <t>2026-10-14 00:25:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:19</t>
+          <t>2026-10-14 00:25:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:19</t>
+          <t>2026-10-14 00:25:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:19</t>
+          <t>2026-10-14 00:25:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:20</t>
+          <t>2026-10-14 00:25:43</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:20</t>
+          <t>2026-10-14 00:25:43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:20</t>
+          <t>2026-10-14 00:25:43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:20</t>
+          <t>2026-10-14 00:25:43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:20</t>
+          <t>2026-10-14 00:25:43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:20</t>
+          <t>2026-10-14 00:25:43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:20</t>
+          <t>2026-10-14 00:25:43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:20</t>
+          <t>2026-10-14 00:25:43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:20</t>
+          <t>2026-10-14 00:25:43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:20</t>
+          <t>2026-10-14 00:25:43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:20</t>
+          <t>2026-10-14 00:25:43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:20</t>
+          <t>2026-10-14 00:25:43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:20</t>
+          <t>2026-10-14 00:25:43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:20</t>
+          <t>2026-10-14 00:25:43</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:20</t>
+          <t>2026-10-14 00:25:43</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:21</t>
+          <t>2026-10-14 00:25:44</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:21</t>
+          <t>2026-10-14 00:25:44</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:21</t>
+          <t>2026-10-14 00:25:44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:21</t>
+          <t>2026-10-14 00:25:44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:21</t>
+          <t>2026-10-14 00:25:44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-14_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:39</t>
+          <t>2026-10-14 22:01:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.97%2490</t>
+          <t>0%2490</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,20 +522,20 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.02%1,112,000</t>
+          <t>14.81%1,416,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.02%</t>
+          <t>14.81%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1112000</v>
+        <v>1416000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:39</t>
+          <t>2026-10-14 22:01:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.47%6070</t>
+          <t>-0.45%5520</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.47%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6070</v>
+        <v>5520</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.28%133,000</t>
+          <t>3.54%152,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.28%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>133000</v>
+        <v>152000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:39</t>
+          <t>2026-10-14 22:01:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.31%211.5</t>
+          <t>-4.78%5780</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-4.78%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>211.5</v>
+        <v>5780</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.59%3,341,000</t>
+          <t>3.54%139,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3341000</v>
+        <v>139000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:39</t>
+          <t>2026-10-14 22:01:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,33 +692,33 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.37%6990</t>
+          <t>+1.14%7070</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6990</v>
+        <v>7070</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.52%99,000</t>
+          <t>3.49%119,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>99000</v>
+        <v>119000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:39</t>
+          <t>2026-10-14 22:01:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>1216統一</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-4.23%2040</t>
+          <t>+1.43%78.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2040</v>
+        <v>78.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.18%301,000</t>
+          <t>3.37%10,393,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.37%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>301000</v>
+        <v>10393000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:39</t>
+          <t>2026-10-14 22:01:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1216統一</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.45%77.1</t>
+          <t>+0.49%2050</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>77.09999999999999</v>
+        <v>2050</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.03%8,045,000</t>
+          <t>3.24%378,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>8045000</v>
+        <v>378000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:39</t>
+          <t>2026-10-14 22:01:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-9.84%5545</t>
+          <t>+2.13%216</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-9.84%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5545</v>
+        <v>216</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.90%95,000</t>
+          <t>3.24%3,650,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>95000</v>
+        <v>3650000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:39</t>
+          <t>2026-10-14 22:01:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>4904遠傳</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-4.91%10060</t>
+          <t>+0.47%108</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>10060</v>
+        <v>108</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.84%54,000</t>
+          <t>3.12%6,914,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>54000</v>
+        <v>6914000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:39</t>
+          <t>2026-10-14 22:01:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4904遠傳</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.9%107.5</t>
+          <t>-0.55%10005</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+1.9%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>107.5</v>
+        <v>10005</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.63%5,022,000</t>
+          <t>2.87%68,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5022000</v>
+        <v>68000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:39</t>
+          <t>2026-10-14 22:01:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.75%141.5</t>
+          <t>+0.14%356</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>141.5</v>
+        <v>356</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.25%3,113,000</t>
+          <t>2.14%1,435,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>3113000</v>
+        <v>1435000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:39</t>
+          <t>2026-10-14 22:01:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-5.82%599</t>
+          <t>+0.56%1785</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.82%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>599</v>
+        <v>1785</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.21%699,000</t>
+          <t>2.01%270,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>699000</v>
+        <v>270000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:39</t>
+          <t>2026-10-14 22:01:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,33 +1180,33 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.1%3280</t>
+          <t>+1.07%3315</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3280</v>
+        <v>3315</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.12%126,000</t>
+          <t>2.00%145,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>126000</v>
+        <v>145000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:39</t>
+          <t>2026-10-14 22:01:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-5.98%1180</t>
+          <t>-2.76%1410</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.98%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1180</v>
+        <v>1410</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.09%335,000</t>
+          <t>1.90%312,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>335000</v>
+        <v>312000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:39</t>
+          <t>2026-10-14 22:01:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.14%355.5</t>
+          <t>+5.69%2880</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>355.5</v>
+        <v>2880</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.08%1,175,000</t>
+          <t>1.83%160,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1175000</v>
+        <v>160000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:39</t>
+          <t>2026-10-14 22:01:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>2412中華電</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-4.92%1450</t>
+          <t>+0.34%148.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-4.92%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1450</v>
+        <v>148.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.95%257,000</t>
+          <t>1.77%2,855,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>257000</v>
+        <v>2855000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:41</t>
+          <t>2026-10-14 22:01:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-9.92%2725</t>
+          <t>+4.67%627</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-9.92%</t>
+          <t>+4.67%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2725</v>
+        <v>627</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.88%125,000</t>
+          <t>1.74%693,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>125000</v>
+        <v>693000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:41</t>
+          <t>2026-10-14 22:01:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>3105穩懋</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-6.58%1775</t>
+          <t>+0.18%557</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.58%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1775</v>
+        <v>557</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.58%168,000</t>
+          <t>1.56%666,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>168000</v>
+        <v>666000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:41</t>
+          <t>2026-10-14 22:01:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>2603長榮</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.22%926</t>
+          <t>-0.38%263</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>926</v>
+        <v>263</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.58%336,000</t>
+          <t>1.54%1,391,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>336000</v>
+        <v>1391000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:41</t>
+          <t>2026-10-14 22:01:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1101台泥</t>
+          <t>2609陽明</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.41%26.35</t>
+          <t>+0.78%65</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>26.35</v>
+        <v>65</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.52%11,318,000</t>
+          <t>1.54%5,672,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>11318000</v>
+        <v>5672000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:41</t>
+          <t>2026-10-14 22:01:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-1.84%240</t>
+          <t>+7.69%1260</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+7.69%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>240</v>
+        <v>1260</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.48%1,223,000</t>
+          <t>1.53%311,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1223000</v>
+        <v>311000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:41</t>
+          <t>2026-10-14 22:01:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1605華新</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-3.99%38.55</t>
+          <t>-1.1%4475</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-3.99%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>38.55</v>
+        <v>4475</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.45%7,283,000</t>
+          <t>1.52%80,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>7283000</v>
+        <v>80000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:41</t>
+          <t>2026-10-14 22:01:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-4.03%2260</t>
+          <t>+0.42%1185</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-4.03%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2260</v>
+        <v>1185</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.41%121,000</t>
+          <t>1.52%307,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>121000</v>
+        <v>307000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:41</t>
+          <t>2026-10-14 22:01:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2412中華電</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.02%148</t>
+          <t>-0.32%923</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>148</v>
+        <v>923</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.37%1,888,000</t>
+          <t>1.51%389,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1888000</v>
+        <v>389000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:41</t>
+          <t>2026-10-14 22:01:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2609陽明</t>
+          <t>2027大成鋼</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+1.42%64.5</t>
+          <t>+2.46%50</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>+2.46%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>64.5</v>
+        <v>50</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.35%4,270,000</t>
+          <t>1.42%6,940,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>4270000</v>
+        <v>6940000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:41</t>
+          <t>2026-10-14 22:01:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.42%718</t>
+          <t>-1.54%480.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>718</v>
+        <v>480.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.31%366,000</t>
+          <t>1.41%690,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>366000</v>
+        <v>690000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:41</t>
+          <t>2026-10-14 22:01:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3105穩懋</t>
+          <t>2610華航</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-4.14%556</t>
+          <t>+0.73%20.65</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-4.14%</t>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>556</v>
+        <v>20.65</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.31%456,000</t>
+          <t>1.41%16,386,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>456000</v>
+        <v>16386000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:41</t>
+          <t>2026-10-14 22:01:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-3.52%2195</t>
+          <t>+0.31%160.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2195</v>
+        <v>160.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.29%114,036</t>
+          <t>1.41%2,104,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>114036</v>
+        <v>2104000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:41</t>
+          <t>2026-10-14 22:01:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>1301台塑</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-5.26%1170</t>
+          <t>+9.89%88.9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>+9.89%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1170</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.26%206,000</t>
+          <t>1.39%4,101,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>206000</v>
+        <v>4101000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:41</t>
+          <t>2026-10-14 22:01:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+3.33%264</t>
+          <t>+0.49%1020</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+3.33%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>264</v>
+        <v>1020</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.25%985,000</t>
+          <t>1.32%310,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>985000</v>
+        <v>310000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:41</t>
+          <t>2026-10-14 22:01:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2027大成鋼</t>
+          <t>1101台泥</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+1.14%48.8</t>
+          <t>+2.66%27.05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+2.66%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>48.8</v>
+        <v>27.05</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.23%5,135,000</t>
+          <t>1.25%11,318,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>5135000</v>
+        <v>11318000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:43</t>
+          <t>2026-10-14 22:01:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1301台塑</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.25%80.9</t>
+          <t>+1.25%243</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>80.90000000000001</v>
+        <v>243</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.21%3,022,000</t>
+          <t>1.23%1,223,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>3022000</v>
+        <v>1223000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:43</t>
+          <t>2026-10-14 22:01:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2610華航</t>
+          <t>1605華新</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.49%20.5</t>
+          <t>+5.58%40.7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+5.58%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>20.5</v>
+        <v>40.7</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.16%11,436,000</t>
+          <t>1.18%7,283,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>11436000</v>
+        <v>7283000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:43</t>
+          <t>2026-10-14 22:01:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.16%4525</t>
+          <t>-1.11%2235</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>4525</v>
+        <v>2235</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.15%50,000</t>
+          <t>1.15%121,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>50000</v>
+        <v>121000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:43</t>
+          <t>2026-10-14 22:01:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-7.4%488</t>
+          <t>-0.56%714</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>488</v>
+        <v>714</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.14%434,000</t>
+          <t>1.10%366,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>434000</v>
+        <v>366000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:43</t>
+          <t>2026-10-14 22:01:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.68%7275</t>
+          <t>-3.64%2115</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>7275</v>
+        <v>2115</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.13%31,000</t>
+          <t>1.05%114,036</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>31000</v>
+        <v>114036</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:43</t>
+          <t>2026-10-14 22:01:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>2377微星</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-7.74%4055</t>
+          <t>+1.27%159</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-7.74%</t>
+          <t>+1.27%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4055</v>
+        <v>159</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.11%51,000</t>
+          <t>1.04%1,576,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>51000</v>
+        <v>1576000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:43</t>
+          <t>2026-10-14 22:01:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-4.48%1600</t>
+          <t>+2.17%165</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-4.48%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1600</v>
+        <v>165</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.06%128,000</t>
+          <t>1.02%1,498,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>128000</v>
+        <v>1498000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:43</t>
+          <t>2026-10-14 22:01:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.89%1040</t>
+          <t>+0.35%142</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.89%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1040</v>
+        <v>142</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.99%189,000</t>
+          <t>1.02%1,717,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>189000</v>
+        <v>1717000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:43</t>
+          <t>2026-10-14 22:01:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.69%1165</t>
+          <t>-2.84%3940</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1165</v>
+        <v>3940</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.98%167,000</t>
+          <t>0.87%51,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>167000</v>
+        <v>51000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:43</t>
+          <t>2026-10-14 22:01:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-8.97%1015</t>
+          <t>+0.96%1050</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-8.97%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1015</v>
+        <v>1050</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.92%167,000</t>
+          <t>0.83%189,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>167000</v>
+        <v>189000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:43</t>
+          <t>2026-10-14 22:01:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7750新代</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-5.22%1815</t>
+          <t>+2.15%1190</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5.22%</t>
+          <t>+2.15%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1815</v>
+        <v>1190</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.92%97,000</t>
+          <t>0.82%167,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>97000</v>
+        <v>167000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:43</t>
+          <t>2026-10-14 22:01:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-2.89%740</t>
+          <t>+0.95%747</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.92%243,000</t>
+          <t>0.76%243,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:43</t>
+          <t>2026-10-14 22:01:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>7750新代</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-5.51%1630</t>
+          <t>+4.13%1890</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-5.51%</t>
+          <t>+4.13%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1630</v>
+        <v>1890</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.77%90,000</t>
+          <t>0.74%97,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>90000</v>
+        <v>97000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:43</t>
+          <t>2026-10-14 22:01:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-2.79%69.7</t>
+          <t>+1.72%70.9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-2.79%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>69.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.77%2,177,000</t>
+          <t>0.64%2,177,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:43</t>
+          <t>2026-10-14 22:01:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.95%160</t>
+          <t>+0.61%1640</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>160</v>
+        <v>1640</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.71%897,000</t>
+          <t>0.62%90,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>897000</v>
+        <v>90000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:44</t>
+          <t>2026-10-14 22:01:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,25 +3254,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0%1440</t>
+          <t>-0.69%1430</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1440</v>
+        <v>1430</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.61%85,000</t>
+          <t>0.51%85,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:44</t>
+          <t>2026-10-14 22:01:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6526達發</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0%783</t>
+          <t>-5.43%6880</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>783</v>
+        <v>6880</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.40%102,000</t>
+          <t>0.49%16,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>102000</v>
+        <v>16000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:44</t>
+          <t>2026-10-14 22:01:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6526達發</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-0.29%1715</t>
+          <t>+2.43%802</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+2.43%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1715</v>
+        <v>802</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.17%20,000</t>
+          <t>0.34%102,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>20000</v>
+        <v>102000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:44</t>
+          <t>2026-10-14 22:01:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2377微星</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+1.29%157</t>
+          <t>-1.75%1685</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+1.29%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>157</v>
+        <v>1685</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.14%20,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:44</t>
+          <t>2026-10-14 22:01:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,30 +3493,30 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-7.18%161.5</t>
+          <t>-3.75%1540</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-7.18%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>161.5</v>
+        <v>1540</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-10-14_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:37</t>
+          <t>2026-10-14 22:31:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:37</t>
+          <t>2026-10-14 22:31:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:37</t>
+          <t>2026-10-14 22:31:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:37</t>
+          <t>2026-10-14 22:31:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:37</t>
+          <t>2026-10-14 22:31:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:37</t>
+          <t>2026-10-14 22:31:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:37</t>
+          <t>2026-10-14 22:31:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:37</t>
+          <t>2026-10-14 22:31:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:37</t>
+          <t>2026-10-14 22:31:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:37</t>
+          <t>2026-10-14 22:31:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:37</t>
+          <t>2026-10-14 22:31:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:37</t>
+          <t>2026-10-14 22:31:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:37</t>
+          <t>2026-10-14 22:31:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:37</t>
+          <t>2026-10-14 22:31:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:37</t>
+          <t>2026-10-14 22:31:41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:38</t>
+          <t>2026-10-14 22:31:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:38</t>
+          <t>2026-10-14 22:31:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:38</t>
+          <t>2026-10-14 22:31:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:38</t>
+          <t>2026-10-14 22:31:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:38</t>
+          <t>2026-10-14 22:31:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:38</t>
+          <t>2026-10-14 22:31:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:38</t>
+          <t>2026-10-14 22:31:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:38</t>
+          <t>2026-10-14 22:31:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:38</t>
+          <t>2026-10-14 22:31:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:38</t>
+          <t>2026-10-14 22:31:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:38</t>
+          <t>2026-10-14 22:31:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:38</t>
+          <t>2026-10-14 22:31:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:38</t>
+          <t>2026-10-14 22:31:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:38</t>
+          <t>2026-10-14 22:31:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:38</t>
+          <t>2026-10-14 22:31:43</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:40</t>
+          <t>2026-10-14 22:31:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:40</t>
+          <t>2026-10-14 22:31:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:40</t>
+          <t>2026-10-14 22:31:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:40</t>
+          <t>2026-10-14 22:31:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:40</t>
+          <t>2026-10-14 22:31:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:40</t>
+          <t>2026-10-14 22:31:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:40</t>
+          <t>2026-10-14 22:31:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:40</t>
+          <t>2026-10-14 22:31:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:40</t>
+          <t>2026-10-14 22:31:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:40</t>
+          <t>2026-10-14 22:31:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:40</t>
+          <t>2026-10-14 22:31:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:40</t>
+          <t>2026-10-14 22:31:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:40</t>
+          <t>2026-10-14 22:31:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:40</t>
+          <t>2026-10-14 22:31:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:40</t>
+          <t>2026-10-14 22:31:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:41</t>
+          <t>2026-10-14 22:31:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:41</t>
+          <t>2026-10-14 22:31:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:41</t>
+          <t>2026-10-14 22:31:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:41</t>
+          <t>2026-10-14 22:31:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:41</t>
+          <t>2026-10-14 22:31:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
